--- a/artfynd/S 758-2023 artfynd.xlsx
+++ b/artfynd/S 758-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538384</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539869</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1045,6 +1060,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828572</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,6 +1186,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828573</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1282,6 +1307,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99123503</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1408,6 +1438,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63202100</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1534,6 +1569,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539589</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1660,6 +1700,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539591</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1786,6 +1831,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539594</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1912,6 +1962,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539595</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2038,6 +2093,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539597</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2164,6 +2224,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539598</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2290,6 +2355,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539599</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2416,6 +2486,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539600</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2542,6 +2617,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539601</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2668,6 +2748,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539653</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2794,6 +2879,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539657</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2920,6 +3010,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98539685</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3046,6 +3141,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189604</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3172,6 +3272,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538321</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3298,6 +3403,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538322</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3424,6 +3534,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538323</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3550,6 +3665,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538324</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3676,6 +3796,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538325</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3802,6 +3927,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538326</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3928,6 +4058,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538327</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4054,6 +4189,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538328</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4180,6 +4320,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538329</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4306,6 +4451,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538330</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4432,6 +4582,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538334</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4558,6 +4713,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538335</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4684,6 +4844,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538336</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4810,6 +4975,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98538337</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4911,6 +5081,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580623</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5012,6 +5187,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580624</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5133,6 +5313,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828559</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5254,6 +5439,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828560</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5375,6 +5565,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828561</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5496,6 +5691,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828562</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5608,6 +5808,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103199876</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5733,6 +5938,11 @@
           <t>FLD0053 Fågelutredningar Kärnebo</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98828497</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5834,6 +6044,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580696</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5935,6 +6150,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580697</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6036,6 +6256,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580681</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6137,6 +6362,11 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580670</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6234,8 +6464,61 @@
           <t>Naturvärdesinventering Kärnebo FNT0006</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98580648</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>